--- a/target/test-classes/dataSheets/1subjectATTestData.xlsx
+++ b/target/test-classes/dataSheets/1subjectATTestData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10215" windowHeight="7680" firstSheet="2" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10215" windowHeight="7680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="mdsPart2" sheetId="1" r:id="rId1"/>
